--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -482,26 +482,22 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6b7a38e7-cead-46b9-8bd4-39a40c726e20</t>
+          <t>bfc79529-0f18-4577-bc50-0d548b08508f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>boseng</t>
+          <t>Siti Aulia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$JacSim1VvdV9YQsj$60645ca974ccc19aa880c4f334d3905e0081977a3d9bd957976acb7345db6130a438d7e75405ab9bcf951b52e7db1a8dbbf7e025a4e0fa7e0f88c63a2907f49b</t>
+          <t>scrypt:32768:8:1$ZypCfNkH0v9ytPDm$6e268e3a35da7b554627a0ea3d83ceae29f6995a15cae9ff0d4a0104a130dd6d641c9dc9498439e96fb6b960617c66741bbed3fced827632991a9ea39f9dd804</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -511,76 +507,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9b6a5ab2-720d-4c05-bb25-0b8629c85dd3</t>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>5167655e-8d9e-4cbd-820a-044265a573ac</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>shidqi</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$s41zrqB7TnxjEOqN$68a53046271ad568ede9904b23716bcd383cb6b521c8aecca4843bc3a407a0e79193f8d5583eda00b8abf0955e5f86275ea051f83f971ae7643afd4daf55351e</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>582f9a5f-a0c9-4737-a724-1fd6f9307798</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>81f1ff59-e353-45d0-93d1-523d8fdd95f6</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>jamang</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$OTvBdjY7XCzWWRNb$dc8b25432475f9baf09cf134dc04add968d27c8df2d5c73da5dfa7a0c63d456b6177e8884d96141653f394a593715d0b252dcb89e850a56ec37b8d93e737002d</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AGT-0003</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -487,17 +487,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bfc79529-0f18-4577-bc50-0d548b08508f</t>
+          <t>6b536775-95d6-4d30-b1b8-11de5d93cd9d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>boseng</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$ZypCfNkH0v9ytPDm$6e268e3a35da7b554627a0ea3d83ceae29f6995a15cae9ff0d4a0104a130dd6d641c9dc9498439e96fb6b960617c66741bbed3fced827632991a9ea39f9dd804</t>
+          <t>scrypt:32768:8:1$jPOimkRSZb7X4GJm$a22587b5a436f9288d12e593c49818263972adf05056a261c18a7e19238b147a4efc2dae8450282fc0610464d9e0653720abc468fc7d2fed6117c4b2b3139186</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -507,12 +507,44 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fc92dceb-43a1-4838-81a3-8f6c17abd948</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$mMRvEAPYsO2gXvrB$611052c6e775181312ac93243f911d7f9be64bf7b759c1a27c0038b1cbb2ac6bc4308a33de1c3b5784b11497a464dbb2a0afd4b089fca1cb489da2ba15279210</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -417,14 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -463,88 +463,200 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>83b7beac-01a8-4036-b72d-13651ef7c06a</t>
+          <t>ad8eb074-f95b-4ae0-a3bd-a1799a0f2868</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>super_admin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$HZUjQyzAm0KqpgmW$556232cc99103619bd2e85eaf5156456329db546dd04a9d4ea0863046dfe62a6eb006514820b66acec61f9a0f86bdbde6f99a58452c1386a9aecf6c0fe06fe32</t>
+          <t>scrypt:32768:8:1$0RNgsbr9TdtGtX7o$45e490962bd8d4a3739b03c3110c98d3ec348201113ee47499977397fa6e9ab4f963e09e9661e3d713a6332871b0c40da6d1d836c606aa880b77b82fe2f0334e</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>super_admin</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6b536775-95d6-4d30-b1b8-11de5d93cd9d</t>
+          <t>d54f1791-4918-4645-b8bf-d34b12a48588</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>boseng</t>
+          <t>bendahara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$jPOimkRSZb7X4GJm$a22587b5a436f9288d12e593c49818263972adf05056a261c18a7e19238b147a4efc2dae8450282fc0610464d9e0653720abc468fc7d2fed6117c4b2b3139186</t>
+          <t>scrypt:32768:8:1$Sqy0YyjspSZKdWum$ae97a903ce9173fa6fae84d331140241cebac68e1bab35c5490b2a63d199ecfd786821783e40b32f9745bf19748c270ac866c845901f775be2a1540adcbc0034</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
-        </is>
-      </c>
+          <t>bendahara</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fc92dceb-43a1-4838-81a3-8f6c17abd948</t>
+          <t>94318062-652f-413e-80b0-796de769ff88</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>septiawan</t>
+          <t>superadmin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$mMRvEAPYsO2gXvrB$611052c6e775181312ac93243f911d7f9be64bf7b759c1a27c0038b1cbb2ac6bc4308a33de1c3b5784b11497a464dbb2a0afd4b089fca1cb489da2ba15279210</t>
+          <t>scrypt:32768:8:1$J6tZAkNwxjtQhMPM$f55318ccb3b1c182568bcaf880fc115861a8fed06e84667b976f9ef7a8cb6176b69e4a535adca99176c5a7441ca96636eab01b7c182398d4024e1303d71a317c</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
-        </is>
-      </c>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>902d7dd6-2ec1-44c2-ab6b-9d92fee95366</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>adminkoperasi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$jhvMG6nKGjyvAuSV$98f6bce43973f4ea9aad483883f2c76ed52825f62a42b99ee410def11ba09027bc3b89e63bbd2b8b33d3882c089f50a34de95297211ee883ee77d748ebb83721</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>admin_koperasi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5dbbea06-6c1c-4b87-99dd-a910b7a196ca</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ketuapengurus</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$2flDApCpsbvKdYK8$ef542c34a5ff6d5846a3e1b330ec7173a9405c866bb0a4f7ce6d12aa8169065c92ce094049906ecda63007d6ef639546fa2da74ea4eef051f9dcd78b61bef7c8</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ketua_pengurus</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>140c391d-e78a-44b9-99a1-8cf164a9fcab</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>anggota_demo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$i4R3FyylxW1RHJvA$62c1b2d1b9e0f03b6b04fb6d6b39e2c2204363d7731a02d427cdf84741c69d11d992f11cd5231226bc487280f15d271333c2daee6b4a19a0d414f7d754cbf80d</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>anggota</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1ea87e2a-ed7c-4f9d-b5c6-ab8b88445a0e</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>auditor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$2V1a79j36R1ba87x$2053a9125e9f11df34b60e997140e76aba304627a78a6fc82048dc9ed0ddef163ac3f8bdeccef45df7235a592d25e089d84936d262403fffeebfd5a5cb6739b5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>auditor</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -463,50 +463,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ad8eb074-f95b-4ae0-a3bd-a1799a0f2868</t>
+          <t>b2c36ee4-8091-46fd-b49a-b86831467dee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>super_admin</t>
+          <t>bendahara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$0RNgsbr9TdtGtX7o$45e490962bd8d4a3739b03c3110c98d3ec348201113ee47499977397fa6e9ab4f963e09e9661e3d713a6332871b0c40da6d1d836c606aa880b77b82fe2f0334e</t>
+          <t>scrypt:32768:8:1$Zv8JFzGoTe9n89Tq$77b3f64a270f3429630e9a65f07f7d631e441a717a3a7c962c61ed29509a14e82fba532766076ffb6660064e267ea4abe766738c4c0c17b622feac6726eac67d</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>super_admin</t>
+          <t>bendahara</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>b2c36ee4-8091-46fd-b49a-b86831467dee</t>
+          <t>7243af4d-02d1-403c-8a4e-e1e65d28138c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bendahara</t>
+          <t>auditor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$Zv8JFzGoTe9n89Tq$77b3f64a270f3429630e9a65f07f7d631e441a717a3a7c962c61ed29509a14e82fba532766076ffb6660064e267ea4abe766738c4c0c17b622feac6726eac67d</t>
+          <t>scrypt:32768:8:1$DPaGvTqZ7SaZiLZa$70c453e8764e3f2ea8489ac0b0b1fc9f37db989d6187a27d925a1885072202037a274595d6c7f307d24cc3ae704a9d41b1c7ed50ddf65bf5f600ac4e7b8c5e53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>bendahara</t>
+          <t>auditor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -519,29 +519,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>02e4a028-e42e-4697-b7b5-da634785e9c8</t>
+          <t>2d340cb7-7557-4aa5-9828-5ca51a09d310</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>boseng</t>
+          <t>superadmin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$VlxAQIQVZE5HHvIi$cdf279722fef284085b227acfc4de61727d684acaf4b3f0bcee5956106404fb87b4002319251a4e3ef6ac3929bd516f0ff1b94c900fdd10c7e4f149589201f69</t>
+          <t>scrypt:32768:8:1$ujuT6B3mlhovDm9A$51d5a811832347c356ba5a913097410f053328fc19f31102786215d553fa67f5ddc2720b27a03ec9ed553b21b1f8fa16f19ce9986aa607f88e985662df54a82e</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anggota</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
-        </is>
-      </c>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-05-04</t>
@@ -551,22 +547,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f5f3446a-ae3e-4fc3-9692-33f1c45af8cb</t>
+          <t>46c0bb31-f298-4425-88f3-aae7ae541d40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ketua_01</t>
+          <t>adminkoperasi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$QwlXiQd3Ey4zHg9A$674b35ea1e98fd54581886e2ba904c39d222d730ddc92b99ad3bdf5227560e0362cacb4702fde7c2e7a3c6a2c310f7ea000d25163c1e3104c6b2efb3752fc74b</t>
+          <t>scrypt:32768:8:1$tLOQUNOswHXFbNlc$4cf32456266763b055f58a557776f96152a12b683bc8970edb75b7c83c3b9640fa10f2008894c526b6cee83511fb5a08033990e523e34f17248f4bb02bf0fe8e</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ketua_pengurus</t>
+          <t>admin_koperasi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -579,22 +575,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7243af4d-02d1-403c-8a4e-e1e65d28138c</t>
+          <t>9530e11b-28ec-4b1f-9d86-f182f6c18c4e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>ketuapengurus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$DPaGvTqZ7SaZiLZa$70c453e8764e3f2ea8489ac0b0b1fc9f37db989d6187a27d925a1885072202037a274595d6c7f307d24cc3ae704a9d41b1c7ed50ddf65bf5f600ac4e7b8c5e53</t>
+          <t>scrypt:32768:8:1$UvDIsieZJOfQ4V6w$09d561c46b57229c52d7ac393737bd0abc6b72e60936b0a7c61da76880df4a0334bcdf7e42b298d8613f8a09e012a6ab9d848b4cf4951453150d8efde70486a5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>ketua_pengurus</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -607,144 +603,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2baddb31-85ea-44f4-b780-b7f9c2479134</t>
+          <t>49f8379a-2c33-4702-acc9-a5e033ce8d99</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>admin_koperasi</t>
+          <t>boseng</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$3bBqGkacm9arJ3oW$3b5687004c090e9c236db8e6aea089e4222e2b08130601a5d8364a4071d1ab6c1f577676f98b3476d4268bf4cd2d235dbbd8eac72dcad9e4ee1994ca35c2988e</t>
+          <t>scrypt:32768:8:1$bCWIhVDTEyG2MYr2$d664026ccbd1da95d970acf402ec5979c464a5dfdcf044eccf2efb30616082bcd177b2e55dcd8212f4e0960d51e0c1f5da3181f9ef362a148147d5fd3cf508e6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>admin_koperasi</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>anggota</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7afc9502-af5e-4bf3-b468-6375c7569652</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2d340cb7-7557-4aa5-9828-5ca51a09d310</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>superadmin</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$ujuT6B3mlhovDm9A$51d5a811832347c356ba5a913097410f053328fc19f31102786215d553fa67f5ddc2720b27a03ec9ed553b21b1f8fa16f19ce9986aa607f88e985662df54a82e</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>super_admin</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>46c0bb31-f298-4425-88f3-aae7ae541d40</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>adminkoperasi</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$tLOQUNOswHXFbNlc$4cf32456266763b055f58a557776f96152a12b683bc8970edb75b7c83c3b9640fa10f2008894c526b6cee83511fb5a08033990e523e34f17248f4bb02bf0fe8e</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>admin_koperasi</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9530e11b-28ec-4b1f-9d86-f182f6c18c4e</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ketuapengurus</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$UvDIsieZJOfQ4V6w$09d561c46b57229c52d7ac393737bd0abc6b72e60936b0a7c61da76880df4a0334bcdf7e42b298d8613f8a09e012a6ab9d848b4cf4951453150d8efde70486a5</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ketua_pengurus</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>f0565388-9982-4523-8656-266f8e5455b2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>anggota_demo</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$KlGD2BqWbAMlCVHh$6cf335f0e826f198161c3e68ae79a8838de9f34081248062a47f93906a8329dc755e4991a2ce8ea559b82defcb76d19329806fe60a6acbfc6eae1e227db77090</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>anggota</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AGT-DEMO-001</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
